--- a/data/Q4-FY26/executive_advisor.xlsx
+++ b/data/Q4-FY26/executive_advisor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prabhakar.sharma\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prabhakar.sharma\Desktop\engine\Q4-FY26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11BD2ED-7CA2-4F7A-9FE8-169C2161BD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06A67F0-CC76-4CC7-BF1B-51D9E678354A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
   <si>
     <t>Record Count</t>
   </si>
@@ -40,12 +40,15 @@
     <t>Google Organic</t>
   </si>
   <si>
+    <t>Direct Traffic</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
     <t>Asif Ahmed</t>
   </si>
   <si>
-    <t>Direct Traffic</t>
-  </si>
-  <si>
     <t>Harsh Chandwani</t>
   </si>
   <si>
@@ -80,9 +83,6 @@
   </si>
   <si>
     <t>Google AdWords Search</t>
-  </si>
-  <si>
-    <t>New</t>
   </si>
   <si>
     <t>Bing Organic</t>
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -637,14 +637,12 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -655,10 +653,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -669,17 +667,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -691,26 +691,26 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -718,21 +718,19 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C11" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="2" t="s">
         <v>4</v>
       </c>
@@ -745,7 +743,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>4</v>
@@ -759,152 +757,154 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="B15" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="D17" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C18" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B19" s="4"/>
       <c r="C19" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="B21" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C21" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D21" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D22" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D23" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D25" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
@@ -912,71 +912,71 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
+      <c r="B28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C28" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D29" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B31" s="4"/>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D31" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D33" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
-      <c r="B34" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B34" s="4"/>
       <c r="C34" s="2" t="s">
         <v>4</v>
       </c>
@@ -986,11 +986,9 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
-      <c r="B35" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B35" s="4"/>
       <c r="C35" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -999,20 +997,22 @@
     <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="B37" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C37" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -1020,111 +1020,109 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="B38" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C38" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D38" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
-      <c r="B40" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B40" s="4"/>
       <c r="C40" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B41" s="4"/>
       <c r="C41" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="B42" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="B43" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C43" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
       <c r="C45" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="B46" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="B46" s="4"/>
       <c r="C46" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="B47" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -1133,70 +1131,72 @@
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4"/>
+      <c r="B50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="B52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
+      <c r="B53" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
       </c>
@@ -1206,11 +1206,9 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
-      <c r="B54" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B54" s="4"/>
       <c r="C54" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -1219,32 +1217,32 @@
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="2" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -1252,71 +1250,75 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
+      <c r="B58" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C58" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D58" s="3">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
+      <c r="B60" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C60" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D60" s="3">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D61" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
-      <c r="B62" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B62" s="4"/>
       <c r="C62" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D62" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D63" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
+      <c r="B64" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C64" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D64" s="3">
         <v>2</v>
@@ -1326,7 +1328,7 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -1334,75 +1336,73 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
-      <c r="B66" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="B66" s="4"/>
       <c r="C66" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D66" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D67" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
+      <c r="B68" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C68" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D68" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D69" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
-      <c r="B70" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="B70" s="4"/>
       <c r="C70" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D70" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D71" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
@@ -1410,9 +1410,7 @@
     </row>
     <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
-      <c r="B73" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B73" s="4"/>
       <c r="C73" s="2" t="s">
         <v>4</v>
       </c>
@@ -1423,10 +1421,10 @@
     <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
@@ -1435,10 +1433,10 @@
     <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
@@ -1446,9 +1444,11 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
+      <c r="B76" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C76" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
@@ -1456,9 +1456,11 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
+      <c r="B77" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C77" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D77" s="3">
         <v>1</v>
@@ -1466,43 +1468,63 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
-      <c r="B78" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B78" s="4"/>
       <c r="C78" s="2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D78" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D79" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
+      <c r="B80" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C80" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D80" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="3">
         <v>1</v>
       </c>
     </row>
